--- a/projekt_sps/calibration.xlsx
+++ b/projekt_sps/calibration.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\plc-control-projects\projekt_sps\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71EB39CB-1771-4BDE-B40C-153967BF4C56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F88EA0-C910-4182-A663-FD7C43F0A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31314FC3-B06D-4768-B34C-651B3AEA3AA5}"/>
   </bookViews>
@@ -75,9 +75,6 @@
     <t>volumen m3</t>
   </si>
   <si>
-    <t>altura calculada_por volumen mm</t>
-  </si>
-  <si>
     <t>gravedad</t>
   </si>
   <si>
@@ -103,6 +100,9 @@
   </si>
   <si>
     <t>y</t>
+  </si>
+  <si>
+    <t>altura calculada_por volumen m</t>
   </si>
 </sst>
 </file>
@@ -118,7 +118,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -128,6 +128,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -144,16 +150,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1379,10 +1387,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="3"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
@@ -1422,7 +1430,7 @@
     </row>
     <row r="8" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C8">
         <v>1000</v>
@@ -1430,9 +1438,9 @@
     </row>
     <row r="9" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>14</v>
-      </c>
-      <c r="C9" s="4">
+        <v>13</v>
+      </c>
+      <c r="C9" s="3">
         <v>9.81</v>
       </c>
     </row>
@@ -1447,10 +1455,10 @@
         <v>8</v>
       </c>
       <c r="H10" t="s">
+        <v>18</v>
+      </c>
+      <c r="I10" t="s">
         <v>19</v>
-      </c>
-      <c r="I10" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="11" spans="2:13" ht="45" x14ac:dyDescent="0.25">
@@ -1473,18 +1481,18 @@
         <v>6</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="2:13" x14ac:dyDescent="0.25">
       <c r="H12" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="I12" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13" spans="2:13" x14ac:dyDescent="0.25">
@@ -1498,16 +1506,16 @@
         <f>C13*(10^-6)</f>
         <v>0</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="5">
         <v>560</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="6">
         <v>-2</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="5">
         <v>-82</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="5">
         <f>D13/$C$6</f>
         <v>0</v>
       </c>
@@ -1570,7 +1578,7 @@
         <v>108</v>
       </c>
       <c r="H15" s="2">
-        <f t="shared" ref="H14:H18" si="2">D15/$C$6</f>
+        <f t="shared" ref="H15:H18" si="2">D15/$C$6</f>
         <v>4.1255651880198196E-2</v>
       </c>
       <c r="I15" s="2">
@@ -1596,13 +1604,13 @@
       <c r="E16">
         <v>817</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="5">
         <v>8080</v>
       </c>
       <c r="G16">
         <v>240</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="5">
         <f t="shared" si="2"/>
         <v>6.1883477820297295E-2</v>
       </c>
@@ -1651,16 +1659,16 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="5">
         <v>973</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="5">
         <v>11920</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="5">
         <v>525</v>
       </c>
-      <c r="H18">
+      <c r="H18" s="5">
         <f t="shared" si="2"/>
         <v>0.1031391297004955</v>
       </c>
@@ -1671,10 +1679,10 @@
     </row>
     <row r="21" spans="2:9" x14ac:dyDescent="0.25">
       <c r="F21" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" t="s">
         <v>21</v>
-      </c>
-      <c r="G21" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.25">

--- a/projekt_sps/calibration.xlsx
+++ b/projekt_sps/calibration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\temp\plc-control-projects\projekt_sps\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1f587cb93711f150/21 Master APE/II Semester/Automatisierung/plc-control-projects/projekt_sps/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7F88EA0-C910-4182-A663-FD7C43F0A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{D7F88EA0-C910-4182-A663-FD7C43F0A4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EE5FC44F-5051-4E21-938E-EA1A6E454FC0}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{31314FC3-B06D-4768-B34C-651B3AEA3AA5}"/>
+    <workbookView xWindow="-104" yWindow="-104" windowWidth="22326" windowHeight="11947" xr2:uid="{31314FC3-B06D-4768-B34C-651B3AEA3AA5}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="23">
   <si>
     <t>area</t>
   </si>
@@ -150,18 +150,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1078,9 +1077,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 – 2022-Design">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 – 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1118,7 +1117,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 – 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1224,7 +1223,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 – 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1366,7 +1365,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1374,25 +1373,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{499B6CF2-ECEB-4A51-B1E9-98F0991120EA}">
-  <dimension ref="B2:M23"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B2:M45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="12" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.59765625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.3984375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.8984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.09765625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="2:13" x14ac:dyDescent="0.3">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4"/>
-    </row>
-    <row r="3" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="C2" s="5"/>
+    </row>
+    <row r="3" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>1</v>
       </c>
@@ -1400,7 +1399,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B4">
         <f>(PI()*(51^2))/(2)</f>
         <v>4085.6412459935259</v>
@@ -1410,7 +1409,7 @@
         <v>5610</v>
       </c>
     </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>9</v>
       </c>
@@ -1418,7 +1417,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B6">
         <f>B4+C4</f>
         <v>9695.6412459935254</v>
@@ -1428,7 +1427,7 @@
         <v>9.6956412459935255E-3</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>14</v>
       </c>
@@ -1436,7 +1435,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>13</v>
       </c>
@@ -1444,7 +1443,7 @@
         <v>9.81</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:13" x14ac:dyDescent="0.3">
       <c r="E10" t="s">
         <v>7</v>
       </c>
@@ -1461,7 +1460,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="2:13" ht="45" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:13" ht="43.2" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>3</v>
       </c>
@@ -1487,7 +1486,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:13" x14ac:dyDescent="0.3">
       <c r="H12" t="s">
         <v>17</v>
       </c>
@@ -1495,7 +1494,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>1</v>
       </c>
@@ -1506,16 +1505,16 @@
         <f>C13*(10^-6)</f>
         <v>0</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="4">
         <v>560</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13">
         <v>-2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>-82</v>
       </c>
-      <c r="H13" s="5">
+      <c r="H13" s="4">
         <f>D13/$C$6</f>
         <v>0</v>
       </c>
@@ -1524,7 +1523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>2</v>
       </c>
@@ -1557,7 +1556,7 @@
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3</v>
       </c>
@@ -1590,7 +1589,7 @@
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>4</v>
       </c>
@@ -1604,13 +1603,13 @@
       <c r="E16">
         <v>817</v>
       </c>
-      <c r="F16" s="5">
+      <c r="F16" s="4">
         <v>8080</v>
       </c>
       <c r="G16">
         <v>240</v>
       </c>
-      <c r="H16" s="5">
+      <c r="H16" s="4">
         <f t="shared" si="2"/>
         <v>6.1883477820297295E-2</v>
       </c>
@@ -1619,7 +1618,7 @@
         <v>607.07691741711642</v>
       </c>
     </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>5</v>
       </c>
@@ -1648,7 +1647,7 @@
         <v>809.43588988948864</v>
       </c>
     </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>6</v>
       </c>
@@ -1659,16 +1658,16 @@
         <f t="shared" si="0"/>
         <v>1E-3</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="4">
         <v>973</v>
       </c>
-      <c r="F18" s="5">
+      <c r="F18" s="4">
         <v>11920</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>525</v>
       </c>
-      <c r="H18" s="5">
+      <c r="H18" s="4">
         <f t="shared" si="2"/>
         <v>0.1031391297004955</v>
       </c>
@@ -1677,7 +1676,7 @@
         <v>1011.7948623618609</v>
       </c>
     </row>
-    <row r="21" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F21" t="s">
         <v>20</v>
       </c>
@@ -1685,7 +1684,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F22">
         <v>-2</v>
       </c>
@@ -1693,7 +1692,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="F23">
         <v>11920</v>
       </c>
@@ -1701,9 +1700,230 @@
         <v>0.1031391297004955</v>
       </c>
     </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B27" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29">
+        <f>(PI()*(51^2))/(2)</f>
+        <v>4085.6412459935259</v>
+      </c>
+      <c r="C29">
+        <f>55*102</f>
+        <v>5610</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B30" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B31">
+        <f>B29+C29</f>
+        <v>9695.6412459935254</v>
+      </c>
+      <c r="C31">
+        <f>B31/1000000</f>
+        <v>9.6956412459935255E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B33" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="34" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B34" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="3">
+        <v>9.81</v>
+      </c>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="E35" t="s">
+        <v>7</v>
+      </c>
+      <c r="F35" t="s">
+        <v>7</v>
+      </c>
+      <c r="G35" t="s">
+        <v>8</v>
+      </c>
+      <c r="H35" t="s">
+        <v>18</v>
+      </c>
+      <c r="I35" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="36" spans="2:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>11</v>
+      </c>
+      <c r="D36" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" t="s">
+        <v>4</v>
+      </c>
+      <c r="F36" t="s">
+        <v>5</v>
+      </c>
+      <c r="G36" t="s">
+        <v>6</v>
+      </c>
+      <c r="H36" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="37" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H37" t="s">
+        <v>17</v>
+      </c>
+      <c r="I37" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B38">
+        <v>1</v>
+      </c>
+      <c r="C38">
+        <v>0</v>
+      </c>
+      <c r="D38">
+        <f>C38*(10^-6)</f>
+        <v>0</v>
+      </c>
+      <c r="E38" s="4">
+        <v>560</v>
+      </c>
+      <c r="F38">
+        <v>-2</v>
+      </c>
+      <c r="G38" s="4">
+        <v>-82</v>
+      </c>
+      <c r="H38" s="4">
+        <f>D38/$C$6</f>
+        <v>0</v>
+      </c>
+      <c r="I38">
+        <f>$C$8*$C$9*H38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B39">
+        <v>4</v>
+      </c>
+      <c r="C39">
+        <v>600</v>
+      </c>
+      <c r="D39">
+        <f t="shared" ref="D39:D40" si="3">C39*(10^-6)</f>
+        <v>5.9999999999999995E-4</v>
+      </c>
+      <c r="E39">
+        <v>817</v>
+      </c>
+      <c r="F39" s="4">
+        <v>8080</v>
+      </c>
+      <c r="G39">
+        <v>240</v>
+      </c>
+      <c r="H39" s="4">
+        <f t="shared" ref="H39:H40" si="4">D39/$C$6</f>
+        <v>6.1883477820297295E-2</v>
+      </c>
+      <c r="I39">
+        <f t="shared" ref="I39:I40" si="5">$C$8*$C$9*H39</f>
+        <v>607.07691741711642</v>
+      </c>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40">
+        <v>6</v>
+      </c>
+      <c r="C40">
+        <v>1000</v>
+      </c>
+      <c r="D40">
+        <f t="shared" si="3"/>
+        <v>1E-3</v>
+      </c>
+      <c r="E40" s="4">
+        <v>973</v>
+      </c>
+      <c r="F40" s="4">
+        <v>11920</v>
+      </c>
+      <c r="G40" s="4">
+        <v>525</v>
+      </c>
+      <c r="H40" s="4">
+        <f t="shared" si="4"/>
+        <v>0.1031391297004955</v>
+      </c>
+      <c r="I40">
+        <f t="shared" si="5"/>
+        <v>1011.7948623618609</v>
+      </c>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>20</v>
+      </c>
+      <c r="G43" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F44">
+        <v>-2</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="F45">
+        <v>11920</v>
+      </c>
+      <c r="G45">
+        <v>0.1031391297004955</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B27:C27"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
